--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:19</t>
+    <t xml:space="preserve">2026-09-09 22:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:18</t>
+    <t xml:space="preserve">2026-09-17 13:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,34 +955,34 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>6.76</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>5.73</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>5.13</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>4.46</v>
+        <v>5.13</v>
       </c>
     </row>
   </sheetData>
@@ -1015,134 +1015,134 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>9.38</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>6.76</v>
+        <v>4.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>8.67</v>
+        <v>5.54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7.96</v>
+        <v>9.38</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>5.73</v>
+        <v>6.76</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>6.99</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>7.42</v>
+        <v>7.96</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5.13</v>
+        <v>5.73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>6.25</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>6.25</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>4.46</v>
+        <v>5.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5.54</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="14">

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:46</t>
+    <t xml:space="preserve">2026-09-25 21:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -530,7 +530,7 @@
         <v>-1.78</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-25.69</v>
+        <v>-25.68</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>5</v>
@@ -553,7 +553,7 @@
         <v>-1.81</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-31.42</v>
+        <v>-31.43</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>5</v>
@@ -576,7 +576,7 @@
         <v>-1.79</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-28.64</v>
+        <v>-28.69</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -599,7 +599,7 @@
         <v>-1.96</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-26.52</v>
+        <v>-26.49</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>4</v>
@@ -622,7 +622,7 @@
         <v>-2.19</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-30.98</v>
+        <v>-31</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>-2.09</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-28.99</v>
+        <v>-29.02</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>
@@ -668,7 +668,7 @@
         <v>-2.18</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-28.87</v>
+        <v>-28.83</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -688,10 +688,10 @@
         <v>7.33</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-2.38</v>
+        <v>-2.37</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-32.47</v>
+        <v>-32.42</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>-2.29</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-30.86</v>
+        <v>-30.9</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>3</v>
@@ -734,10 +734,10 @@
         <v>7.67</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-1.96</v>
+        <v>-1.95</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-25.55</v>
+        <v>-25.45</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
@@ -760,7 +760,7 @@
         <v>-2.45</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-29.91</v>
+        <v>-29.93</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -783,7 +783,7 @@
         <v>-2.23</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-28.02</v>
+        <v>-28.06</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -806,7 +806,7 @@
         <v>-2.28</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-26.67</v>
+        <v>-26.7</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
@@ -829,7 +829,7 @@
         <v>-2.89</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-28.73</v>
+        <v>-28.75</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -849,10 +849,10 @@
         <v>9.38</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-2.62</v>
+        <v>-2.61</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-27.93</v>
+        <v>-27.88</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringrmin_a_2023_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringrmin_a_2023_maule.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:41</t>
+    <t xml:space="preserve">2026-10-05 07:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
